--- a/Result/profitability/1593.xlsx
+++ b/Result/profitability/1593.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM65"/>
+  <dimension ref="A1:AM66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.675</v>
+        <v>0.85625</v>
       </c>
       <c r="N2" t="n">
-        <v>30.23125</v>
+        <v>29.67875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7737499999999999</v>
+        <v>0.9412499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>29.01125</v>
+        <v>28.7775</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6237499999999999</v>
+        <v>0.825</v>
       </c>
       <c r="N4" t="n">
-        <v>27.32125</v>
+        <v>27.07</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -8689,6 +8689,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1593</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>342</v>
+      </c>
+      <c r="D66" t="n">
+        <v>241</v>
+      </c>
+      <c r="E66" t="n">
+        <v>102</v>
+      </c>
+      <c r="F66" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="G66" t="n">
+        <v>23</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6.81%</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>112</v>
+      </c>
+      <c r="J66" t="n">
+        <v>135</v>
+      </c>
+      <c r="K66" t="n">
+        <v>81</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="N66" t="n">
+        <v>31.43125</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>-0.03321393682839469</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>3.613636363636363</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>-3.260000000000002</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>-0.09893778452200308</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
